--- a/GameData/GameData_Player.xlsx
+++ b/GameData/GameData_Player.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41843B9D-146B-4555-9D26-7132448F7BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9491149E-B831-467D-A86C-0F3F383EA65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="1420" windowWidth="20360" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5120" yWindow="2100" windowWidth="20360" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skeleton" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>LV</t>
   </si>
@@ -42,19 +42,27 @@
   </si>
   <si>
     <t>플레이어</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>NeedExp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Hp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Timer</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Dot ATK</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>Druation</t>
+  </si>
+  <si>
+    <t>Knockback</t>
   </si>
 </sst>
 </file>
@@ -64,7 +72,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -108,6 +116,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="7">
@@ -225,7 +241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -276,7 +292,21 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -499,12 +529,14 @@
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="11"/>
+    <col min="7" max="7" width="14" style="19" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="20"/>
+    <col min="9" max="9" width="8.6640625" style="22"/>
+    <col min="10" max="10" width="13.4140625" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -522,9 +554,18 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="11"/>
+      <c r="G1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
@@ -535,23 +576,32 @@
     <row r="2" spans="1:16" ht="22" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5">
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E2" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F2" s="9">
-        <v>60</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20">
+        <v>0</v>
+      </c>
+      <c r="I2" s="21">
+        <v>0</v>
+      </c>
+      <c r="J2" s="20">
+        <v>0</v>
+      </c>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
@@ -562,23 +612,32 @@
     <row r="3" spans="1:16" ht="22" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" s="12">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E3" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F3" s="9">
-        <v>60</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="G3" s="16">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20">
+        <v>1</v>
+      </c>
+      <c r="I3" s="21">
+        <v>1</v>
+      </c>
+      <c r="J3" s="20">
+        <v>1</v>
+      </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
@@ -589,23 +648,32 @@
     <row r="4" spans="1:16" ht="22" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="12">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="E4" s="6">
-        <v>27.9</v>
+        <v>2</v>
       </c>
       <c r="F4" s="9">
-        <v>60</v>
-      </c>
-      <c r="G4" s="16"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="11"/>
+        <v>2</v>
+      </c>
+      <c r="G4" s="16">
+        <v>2</v>
+      </c>
+      <c r="H4" s="20">
+        <v>2</v>
+      </c>
+      <c r="I4" s="21">
+        <v>2</v>
+      </c>
+      <c r="J4" s="20">
+        <v>2</v>
+      </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -616,23 +684,32 @@
     <row r="5" spans="1:16" ht="22" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="12">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="E5" s="6">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F5" s="9">
-        <v>60</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="G5" s="16">
+        <v>3</v>
+      </c>
+      <c r="H5" s="20">
+        <v>3</v>
+      </c>
+      <c r="I5" s="21">
+        <v>3</v>
+      </c>
+      <c r="J5" s="20">
+        <v>3</v>
+      </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
@@ -643,23 +720,32 @@
     <row r="6" spans="1:16" ht="22" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5">
         <v>68</v>
       </c>
       <c r="D6" s="12">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="E6" s="6">
-        <v>31.6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="9">
-        <v>60</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="16">
+        <v>4</v>
+      </c>
+      <c r="H6" s="20">
+        <v>4</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4</v>
+      </c>
+      <c r="J6" s="20">
+        <v>4</v>
+      </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
@@ -670,23 +756,32 @@
     <row r="7" spans="1:16" ht="22" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D7" s="12">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="6">
-        <v>32.9</v>
+        <v>5</v>
       </c>
       <c r="F7" s="9">
-        <v>60</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="11"/>
+        <v>5</v>
+      </c>
+      <c r="G7" s="16">
+        <v>5</v>
+      </c>
+      <c r="H7" s="20">
+        <v>5</v>
+      </c>
+      <c r="I7" s="21">
+        <v>5</v>
+      </c>
+      <c r="J7" s="20">
+        <v>5</v>
+      </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
@@ -697,23 +792,32 @@
     <row r="8" spans="1:16" ht="22" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D8" s="12">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="E8" s="6">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F8" s="9">
-        <v>60</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="11"/>
+        <v>6</v>
+      </c>
+      <c r="G8" s="16">
+        <v>6</v>
+      </c>
+      <c r="H8" s="20">
+        <v>6</v>
+      </c>
+      <c r="I8" s="21">
+        <v>6</v>
+      </c>
+      <c r="J8" s="20">
+        <v>6</v>
+      </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
@@ -724,23 +828,32 @@
     <row r="9" spans="1:16" ht="22" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="D9" s="12">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="E9" s="6">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F9" s="9">
-        <v>60</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="G9" s="16">
+        <v>7</v>
+      </c>
+      <c r="H9" s="20">
+        <v>7</v>
+      </c>
+      <c r="I9" s="21">
+        <v>7</v>
+      </c>
+      <c r="J9" s="20">
+        <v>7</v>
+      </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
@@ -751,23 +864,32 @@
     <row r="10" spans="1:16" ht="22" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D10" s="12">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="E10" s="6">
-        <v>35.799999999999997</v>
+        <v>8</v>
       </c>
       <c r="F10" s="9">
-        <v>60</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="11"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="16">
+        <v>8</v>
+      </c>
+      <c r="H10" s="20">
+        <v>8</v>
+      </c>
+      <c r="I10" s="21">
+        <v>8</v>
+      </c>
+      <c r="J10" s="20">
+        <v>8</v>
+      </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
@@ -778,23 +900,32 @@
     <row r="11" spans="1:16" ht="22" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="D11" s="12">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="E11" s="6">
-        <v>36.6</v>
+        <v>9</v>
       </c>
       <c r="F11" s="9">
-        <v>60</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="11"/>
+        <v>9</v>
+      </c>
+      <c r="G11" s="16">
+        <v>9</v>
+      </c>
+      <c r="H11" s="20">
+        <v>9</v>
+      </c>
+      <c r="I11" s="21">
+        <v>9</v>
+      </c>
+      <c r="J11" s="20">
+        <v>9</v>
+      </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
@@ -805,23 +936,32 @@
     <row r="12" spans="1:16" ht="22" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="D12" s="12">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E12" s="6">
-        <v>37.299999999999997</v>
+        <v>10</v>
       </c>
       <c r="F12" s="9">
-        <v>60</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="11"/>
+        <v>10</v>
+      </c>
+      <c r="G12" s="16">
+        <v>10</v>
+      </c>
+      <c r="H12" s="20">
+        <v>10</v>
+      </c>
+      <c r="I12" s="21">
+        <v>10</v>
+      </c>
+      <c r="J12" s="20">
+        <v>10</v>
+      </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
@@ -832,23 +972,32 @@
     <row r="13" spans="1:16" ht="22" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="E13" s="6">
-        <v>37.9</v>
+        <v>11</v>
       </c>
       <c r="F13" s="9">
-        <v>60</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="G13" s="16">
+        <v>11</v>
+      </c>
+      <c r="H13" s="20">
+        <v>11</v>
+      </c>
+      <c r="I13" s="21">
+        <v>11</v>
+      </c>
+      <c r="J13" s="20">
+        <v>11</v>
+      </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
@@ -859,23 +1008,32 @@
     <row r="14" spans="1:16" ht="22" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5">
-        <v>356</v>
+        <v>452</v>
       </c>
       <c r="D14" s="12">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="E14" s="6">
-        <v>38.5</v>
+        <v>12</v>
       </c>
       <c r="F14" s="9">
-        <v>60</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="11"/>
+        <v>12</v>
+      </c>
+      <c r="G14" s="16">
+        <v>12</v>
+      </c>
+      <c r="H14" s="20">
+        <v>12</v>
+      </c>
+      <c r="I14" s="21">
+        <v>12</v>
+      </c>
+      <c r="J14" s="20">
+        <v>12</v>
+      </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
@@ -886,23 +1044,32 @@
     <row r="15" spans="1:16" ht="22" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="5">
-        <v>410</v>
+        <v>527</v>
       </c>
       <c r="D15" s="12">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="6">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F15" s="9">
-        <v>60</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="11"/>
+        <v>13</v>
+      </c>
+      <c r="G15" s="16">
+        <v>13</v>
+      </c>
+      <c r="H15" s="20">
+        <v>13</v>
+      </c>
+      <c r="I15" s="21">
+        <v>13</v>
+      </c>
+      <c r="J15" s="20">
+        <v>13</v>
+      </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
@@ -913,23 +1080,32 @@
     <row r="16" spans="1:16" ht="22" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="5">
-        <v>468</v>
+        <v>608</v>
       </c>
       <c r="D16" s="12">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="E16" s="6">
-        <v>39.5</v>
+        <v>14</v>
       </c>
       <c r="F16" s="9">
-        <v>60</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="11"/>
+        <v>14</v>
+      </c>
+      <c r="G16" s="16">
+        <v>14</v>
+      </c>
+      <c r="H16" s="20">
+        <v>14</v>
+      </c>
+      <c r="I16" s="21">
+        <v>14</v>
+      </c>
+      <c r="J16" s="20">
+        <v>14</v>
+      </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
@@ -940,23 +1116,32 @@
     <row r="17" spans="1:16" ht="22" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5">
-        <v>530</v>
+        <v>695</v>
       </c>
       <c r="D17" s="12">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E17" s="6">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F17" s="9">
-        <v>60</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="11"/>
+        <v>15</v>
+      </c>
+      <c r="G17" s="16">
+        <v>15</v>
+      </c>
+      <c r="H17" s="20">
+        <v>15</v>
+      </c>
+      <c r="I17" s="21">
+        <v>15</v>
+      </c>
+      <c r="J17" s="20">
+        <v>15</v>
+      </c>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
@@ -967,23 +1152,32 @@
     <row r="18" spans="1:16" ht="22" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5">
-        <v>596</v>
+        <v>788</v>
       </c>
       <c r="D18" s="12">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="E18" s="6">
-        <v>40.4</v>
+        <v>16</v>
       </c>
       <c r="F18" s="9">
-        <v>60</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="G18" s="16">
+        <v>16</v>
+      </c>
+      <c r="H18" s="20">
+        <v>16</v>
+      </c>
+      <c r="I18" s="21">
+        <v>16</v>
+      </c>
+      <c r="J18" s="20">
+        <v>16</v>
+      </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
@@ -994,23 +1188,32 @@
     <row r="19" spans="1:16" ht="22" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5">
-        <v>666</v>
+        <v>887</v>
       </c>
       <c r="D19" s="12">
-        <v>2700</v>
+        <v>2200</v>
       </c>
       <c r="E19" s="6">
-        <v>40.799999999999997</v>
+        <v>17</v>
       </c>
       <c r="F19" s="9">
-        <v>60</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="11"/>
+        <v>17</v>
+      </c>
+      <c r="G19" s="16">
+        <v>17</v>
+      </c>
+      <c r="H19" s="20">
+        <v>17</v>
+      </c>
+      <c r="I19" s="21">
+        <v>17</v>
+      </c>
+      <c r="J19" s="20">
+        <v>17</v>
+      </c>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
@@ -1021,23 +1224,32 @@
     <row r="20" spans="1:16" ht="22" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="5">
-        <v>740</v>
+        <v>992</v>
       </c>
       <c r="D20" s="12">
-        <v>2800</v>
+        <v>2300</v>
       </c>
       <c r="E20" s="6">
-        <v>41.2</v>
+        <v>18</v>
       </c>
       <c r="F20" s="9">
-        <v>60</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="11"/>
+        <v>18</v>
+      </c>
+      <c r="G20" s="16">
+        <v>18</v>
+      </c>
+      <c r="H20" s="20">
+        <v>18</v>
+      </c>
+      <c r="I20" s="21">
+        <v>18</v>
+      </c>
+      <c r="J20" s="20">
+        <v>18</v>
+      </c>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
@@ -1048,23 +1260,32 @@
     <row r="21" spans="1:16" ht="22" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="5">
-        <v>818</v>
+        <v>1103</v>
       </c>
       <c r="D21" s="12">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="E21" s="6">
-        <v>41.6</v>
+        <v>19</v>
       </c>
       <c r="F21" s="9">
-        <v>60</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="11"/>
+        <v>19</v>
+      </c>
+      <c r="G21" s="16">
+        <v>19</v>
+      </c>
+      <c r="H21" s="20">
+        <v>19</v>
+      </c>
+      <c r="I21" s="21">
+        <v>19</v>
+      </c>
+      <c r="J21" s="20">
+        <v>19</v>
+      </c>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
@@ -1074,14 +1295,33 @@
     </row>
     <row r="22" spans="1:16" ht="28" customHeight="1">
       <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="17"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="3">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1220</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>20</v>
+      </c>
+      <c r="F22" s="10">
+        <v>20</v>
+      </c>
+      <c r="G22" s="17">
+        <v>20</v>
+      </c>
+      <c r="H22" s="17">
+        <v>20</v>
+      </c>
+      <c r="I22" s="17">
+        <v>20</v>
+      </c>
+      <c r="J22" s="17">
+        <v>20</v>
+      </c>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
